--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/KENTUCKY_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/KENTUCKY_2016.xlsx
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C142">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C217">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C486">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C537">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 26-</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C538">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C555">
